--- a/docs/sitemap_document.xlsx
+++ b/docs/sitemap_document.xlsx
@@ -75,13 +75,13 @@
     <t xml:space="preserve">第2階層</t>
   </si>
   <si>
-    <t xml:space="preserve">ペットライフプラスとは / サービス詳細 / 活用情報 / サポート</t>
+    <t xml:space="preserve">サービス紹介（f_service） / ご利用の流れ（f_flow） / 運営情報（f_info） / お問い合わせ（f_contact） / Webアプリ紹介（webapp）</t>
   </si>
   <si>
     <t xml:space="preserve">第3階層</t>
   </si>
   <si>
-    <t xml:space="preserve">コンセプト / 提供価値 / 健康管理機能 / 医療サポート / 料金 / ご利用の流れ / 事例・お客様の声 / コラム / FAQ / お問い合わせ / 特商法・プライバシー</t>
+    <t xml:space="preserve">健康管理機能 / AI症状チェック / オンライン診療・訪問ケア / 登録手順 / 初期設定 / 利用開始フロー / コンセプト / ミッション / 利用規約・プライバシー / 問い合わせフォーム / 返信目安 / 機能概要 / 主要画面導線</t>
   </si>
   <si>
     <t xml:space="preserve">Webアプリ(ログイン前)</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">サービス紹介</t>
+    <t xml:space="preserve">サービス紹介（f_service）</t>
   </si>
   <si>
     <t xml:space="preserve">提供機能と利用メリットを具体的に説明する</t>
@@ -132,13 +132,13 @@
     <t xml:space="preserve">3</t>
   </si>
   <si>
-    <t xml:space="preserve">料金・プラン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">料金体系を明確にし、比較検討しやすくする</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プラン比較表、オプション、支払い方法、利用条件</t>
+    <t xml:space="preserve">ご利用の流れ（f_flow）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込みから利用開始後までの手順を可視化する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">登録手順、初期設定、利用開始フロー、サポート案内</t>
   </si>
   <si>
     <t xml:space="preserve">4</t>
@@ -156,61 +156,61 @@
     <t xml:space="preserve">5</t>
   </si>
   <si>
-    <t xml:space="preserve">事例・お客様の声</t>
-  </si>
-  <si>
-    <t xml:space="preserve">利用イメージと信頼性を高める</t>
-  </si>
-  <si>
-    <t xml:space="preserve">導入事例、ビフォーアフター、ユーザーコメント</t>
+    <t xml:space="preserve">運営情報（f_info）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">運営体制と理念・方針を示し、安心感を与える</t>
+  </si>
+  <si>
+    <t xml:space="preserve">運営者情報、コンセプト、ミッション、利用規約・プライバシー</t>
   </si>
   <si>
     <t xml:space="preserve">6</t>
   </si>
   <si>
-    <t xml:space="preserve">FAQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不安や疑問を事前に解消し、離脱を防ぐ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">よくある質問、利用条件、対応時間、トラブル時の案内</t>
+    <t xml:space="preserve">お問い合わせ（f_contact）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">問い合わせ・相談を受け付ける</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フォーム、連絡先、返信目安</t>
   </si>
   <si>
     <t xml:space="preserve">7</t>
   </si>
   <si>
-    <t xml:space="preserve">お問い合わせ・申込み</t>
-  </si>
-  <si>
-    <t xml:space="preserve">問い合わせ・相談・申込みを受け付ける</t>
-  </si>
-  <si>
-    <t xml:space="preserve">フォーム、無料相談予約、連絡先、返信目安</t>
+    <t xml:space="preserve">Webアプリ紹介（webapp）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アプリ機能と主要画面を案内する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">機能概要、主要画面、ログイン導線</t>
   </si>
   <si>
     <t xml:space="preserve">8</t>
   </si>
   <si>
-    <t xml:space="preserve">運営者情報（About）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">運営体制と理念を示し、安心感を与える</t>
-  </si>
-  <si>
-    <t xml:space="preserve">会社/運営者情報、コンセプト、ミッション、実績</t>
+    <t xml:space="preserve">Webアプリ紹介（webapp）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webアプリ紹介（webapp）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webアプリ紹介（webapp）</t>
   </si>
   <si>
     <t xml:space="preserve">9</t>
   </si>
   <si>
-    <t xml:space="preserve">特商法・プライバシーポリシー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">法令順守と個人情報保護方針を明示する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">特商法表記、個人情報の取扱い、利用規約リンク</t>
+    <t xml:space="preserve">Webアプリ紹介（webapp）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webアプリ紹介（webapp）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webアプリ紹介（webapp）</t>
   </si>
   <si>
     <t xml:space="preserve">画面名</t>
@@ -354,34 +354,34 @@
     <t xml:space="preserve">サービス紹介ページ</t>
   </si>
   <si>
-    <t xml:space="preserve">料金を確認する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">料金と他サービス比較を行う</t>
-  </si>
-  <si>
-    <t xml:space="preserve">料金・プランページ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">利用開始を判断する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">口コミや利用事例で安心材料を確認する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">事例・お客様の声ページ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">登録/申込みへ進む</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不明点を解消する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAQページ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">申込みフォームへ進む</t>
+    <t xml:space="preserve">利用の流れを確認する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">登録〜利用開始までの手順を確認する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ご利用の流れページ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">運営情報を確認する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">運営体制・利用方針を確認する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">運営情報ページ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">問い合わせ/相談へ進む</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不明点を問い合わせる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">お問い合わせページ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webアプリ詳細を確認する</t>
   </si>
   <si>
     <t xml:space="preserve">新規登録を行う</t>
@@ -441,16 +441,16 @@
     <t xml:space="preserve">AI症状チェックと相談の流れ確認</t>
   </si>
   <si>
-    <t xml:space="preserve">料金確認</t>
-  </si>
-  <si>
-    <t xml:space="preserve">単発利用可否・相談料金を確認</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAQで確認</t>
-  </si>
-  <si>
-    <t xml:space="preserve">夜間相談可否・受診目安を確認</t>
+    <t xml:space="preserve">利用の流れを確認する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">利用開始手順と必要情報を確認する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不安点を問い合わせる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">夜間相談可否や受診目安を問い合わせる</t>
   </si>
   <si>
     <t xml:space="preserve">相談申込み</t>
@@ -519,46 +519,46 @@
     <t xml:space="preserve">サービス概要・導線表示</t>
   </si>
   <si>
-    <t xml:space="preserve">/services</t>
+    <t xml:space="preserve">/f_service.html</t>
   </si>
   <si>
     <t xml:space="preserve">機能・提供価値の説明</t>
   </si>
   <si>
-    <t xml:space="preserve">/plans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プラン比較、料金表示</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/flow</t>
+    <t xml:space="preserve">/f_flow.html</t>
   </si>
   <si>
     <t xml:space="preserve">登録〜利用開始までの手順</t>
   </si>
   <si>
-    <t xml:space="preserve">/cases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">導入事例・レビュー表示</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/faq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">よくある質問表示</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/about</t>
-  </si>
-  <si>
-    <t xml:space="preserve">運営者情報</t>
-  </si>
-  <si>
-    <t xml:space="preserve">企業/運営情報表示</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/contact</t>
+    <t xml:space="preserve">/f_flow.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">登録〜利用開始までの手順</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/f_info.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">運営情報・利用規約・プライバシー表示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/f_contact.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">問い合わせ入力画面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/webapp.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">運営情報</t>
+  </si>
+  <si>
+    <t xml:space="preserve">運営情報・利用規約・プライバシー表示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/f_contact.html</t>
   </si>
   <si>
     <t xml:space="preserve">お問い合わせフォーム</t>
@@ -576,13 +576,13 @@
     <t xml:space="preserve">問い合わせ内容を送信</t>
   </si>
   <si>
-    <t xml:space="preserve">/legal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">特商法・プライバシー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">法務情報表示</t>
+    <t xml:space="preserve">/webapp.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webアプリ紹介</t>
+  </si>
+  <si>
+    <t xml:space="preserve">主要機能・画面導線を表示</t>
   </si>
   <si>
     <t xml:space="preserve">/app/login</t>
